--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_959_USA_Alaska_Subarctic.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_959_USA_Alaska_Subarctic.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R740381931133486d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R408e7b67d27f4632"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R3a3c1b2fdd1d410d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R018ad35269d945e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rdf2230f9b5cb442e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R185ccda95c1f4cb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R4aea8ae272e64edc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R9985a869397e4950"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R77f61cecab984ef1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rbd28d1f60ffb4de4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rc1d6fc85103e414b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rd00e642f9dd44d7d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ959CommercialTable" displayName="EEZ959CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ959CommercialTable" displayName="EEZ959CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ959FunctionalTable" displayName="EEZ959FunctionalTable" ref="A1:O19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O19"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ959FunctionalTable" displayName="EEZ959FunctionalTable" ref="A1:E19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E19"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ959ValidationTable" displayName="EEZ959ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ959ValidationTable" displayName="EEZ959ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6188,7 +6142,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e04b2e677f84736"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44c5fa3c12d74e00"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6198,20 +6152,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6219,606 +6163,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1744383.2864033554</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.6423553990182342</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>438.88971031970726</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1744383.2864033554</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>503.23439862327143</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$83,A2,'Species'!$U$2:$U$83))</x:f>
-        <x:v>877833674.1016784</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.6423553990182342</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>438.88971031970726</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>765591875.2561076</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>112241798.8455708</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1466078761716527</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.14660787617165272</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>22568.307642596803</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.412757548060949</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>258.67684065584666</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>22568.307642596803</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>367.8764439609008</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$83,A3,'Species'!$U$2:$U$83))</x:f>
-        <x:v>8302348.761774132</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.412757548060949</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>258.67684065584666</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>5837898.51993614</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>2464450.2418379923</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.4221468107782302</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.4221468107782303</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>229707.65162622966</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.6661341310098874</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>463.5900765258681</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>229707.65162622966</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>600.9339108474718</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$83,A4,'Species'!$U$2:$U$83))</x:f>
-        <x:v>138039117.4433388</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.6661341310098874</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>463.5900765258681</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>106490187.79598126</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>31548929.647357553</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2962613767552034</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.29626137675520325</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>23769.6659945</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.1600000000000006</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>144.54397707459296</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>23769.6659945</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$83,A5,'Species'!$U$2:$U$83))</x:f>
-        <x:v>3435762.0565797356</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.1600000000000006</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>144.54397707459296</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>3435762.05657974</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>-4.190951585769653e-9</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>0.9999999999999988</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>-1.2198026279915599e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>522.2202270281999</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.023830537617625</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>10.564052178213071</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>522.2202270281999</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>10.874676574582098</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$83,A6,'Species'!$U$2:$U$83))</x:f>
-        <x:v>5678.976069636511</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.023830537617625</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>10.564052178213071</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>5516.76172684418</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>162.21434279233108</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.029403905918758</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.02940390591875798</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>40659.0136312983</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.301088050526329</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>200.02673703913743</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>40659.0136312983</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>220.41693005192138</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$83,A7,'Species'!$U$2:$U$83))</x:f>
-        <x:v>8961934.963549996</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.301088050526329</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>200.02673703913743</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>8132889.827898409</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>829045.1356515866</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1019373375510015</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.1019373375510015</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1.310594878</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.2108128246324483</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>162.48483159768702</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1.310594878</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>163.46412684250072</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$83,A8,'Species'!$U$2:$U$83))</x:f>
-        <x:v>214.23524737652377</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.2108128246324483</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>162.48483159768702</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>212.95178804462117</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1.2834593319026055</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0060269948596707</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.00602699485967065</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>383751.11837248836</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.047211028233561</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1114.8361125352524</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>383751.11837248836</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1732.2827011676166</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$83,A9,'Species'!$U$2:$U$83))</x:f>
-        <x:v>664765423.9103879</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.047211028233561</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1114.8361125352524</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>427819604.9874404</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>236945818.92294747</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.5538451631497896</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.5538451631497896</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>167667.8378751983</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.525233749695622</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>335.1457756521194</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>167667.8378751983</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>365.80392199789117</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$83,A10,'Species'!$U$2:$U$83))</x:f>
-        <x:v>61333552.6876541</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.525233749695622</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>335.1457756521194</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>56193167.57659715</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>5140385.111056954</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0914770484160743</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0914770484160743</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>27154.780734861</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.8326511101819</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>680.2226832693401</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>27154.780734861</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>686.7912911254392</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$83,A11,'Species'!$U$2:$U$83))</x:f>
-        <x:v>18649666.92112339</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.8326511101819</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>680.2226832693401</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>18471297.815057732</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>178369.106065657</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0096565551512169</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.009656555151216889</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re71e8c065d3943ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re960aaf2caad42ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6828,20 +6378,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6849,1038 +6389,364 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1554.8986418370002</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.923215151111318</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>837.9443000592299</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1554.8986418370002</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>984.7159090605841</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$83,A2,'Species'!$U$2:$U$83))</x:f>
-        <x:v>1531133.4295935892</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.923215151111318</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>837.9443000592299</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1302918.4540971525</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>228214.9754964367</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1751567604087523</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.17515676040875217</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>14410.9699684572</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.84</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>691.8309709189363</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>14410.9699684572</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>691.8309709189363</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$83,A3,'Species'!$U$2:$U$83))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>9969955.345161377</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.84</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>691.8309709189363</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>9969955.345161377</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>57226.0286710773</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.787864212449767</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>613.5701348668697</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>57226.0286710773</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>691.8902131018386</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$83,A4,'Species'!$U$2:$U$83))</x:f>
-        <x:v>39594129.1722036</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.787864212449767</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>613.5701348668697</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>35112182.12960825</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>4481947.042595349</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1276464967643227</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.12764649676432271</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>228395.956191686</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.163934871501677</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1458.5955071887813</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>228395.956191686</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1459.5985612529082</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$83,A5,'Species'!$U$2:$U$83))</x:f>
-        <x:v>333366409.05336714</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.163934871501677</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1458.5955071887813</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>333137315.56127894</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>229093.49208819866</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0006876848716337</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0006876848716338356</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>14887.573738812001</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.14274641966882</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1389.141288258489</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>14887.573738812001</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1390.9387219244513</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$83,A6,'Species'!$U$2:$U$83))</x:f>
-        <x:v>20707702.78881919</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.14274641966882</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1389.141288258489</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>20680943.362576555</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>26759.426242634654</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0012939170991135</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.001293917099113452</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>23604.900364694</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.82</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>660.6934480075957</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>23604.900364694</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>660.6934480075957</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$83,A7,'Species'!$U$2:$U$83))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>15595603.011825433</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.82</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>660.6934480075957</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>15595603.011825433</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>24151.579848712103</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.795306386928191</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>624.1750244195445</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>24151.579848712103</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>624.3049770222348</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$83,A8,'Species'!$U$2:$U$83))</x:f>
-        <x:v>15077951.502500877</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.795306386928191</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>624.1750244195445</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>15074812.941840455</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>3138.5606604218483</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0002081989788218</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.00020819897882186705</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1658.832323459</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.049896101361837</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1121.750059812081</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1658.832323459</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1121.8091359482817</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$83,A9,'Species'!$U$2:$U$83))</x:f>
-        <x:v>1860893.255462621</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.049896101361837</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1121.750059812081</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1860795.2580583466</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>97.99740427453071</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0000526642594612</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.000052664259461186744</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>22326.1981169968</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.4204868260564485</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>263.32180660953105</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>22326.1981169968</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>371.32226893238106</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$83,A10,'Species'!$U$2:$U$83))</x:f>
-        <x:v>8290214.541437105</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.4204868260564485</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>263.32180660953105</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>5878974.822889907</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>2411239.718547198</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.410146291009614</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.41014629100961403</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1530512.8035051622</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.570032653345878</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>371.56316480655556</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1530512.8035051622</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>371.6181834763335</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$83,A11,'Species'!$U$2:$U$83))</x:f>
-        <x:v>568766387.825859</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.570032653345878</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>371.56316480655556</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>568682181.0473319</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>84206.77852702141</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0001480735309343</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.00014807353093416656</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>347564.0238402582</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.9641851399418933</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>920.8420434880155</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>347564.0238402582</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1722.3101087315379</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$83,A12,'Species'!$U$2:$U$83))</x:f>
-        <x:v>598613031.6914859</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.9641851399418933</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>920.8420434880155</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>320051565.9559807</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>278561465.73550516</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.870364326771699</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.870364326771699</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>156227.55206195428</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.4821998097909064</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>303.5287335101149</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>156227.55206195428</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>315.9917178886038</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$83,A13,'Species'!$U$2:$U$83))</x:f>
-        <x:v>49366612.55758822</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.4821998097909064</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>303.5287335101149</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>47419551.01675052</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>1947061.5408376977</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0410603116033283</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.04106031160332826</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>12.45258727</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.38</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>2398.83291901949</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>12.45258727</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>2398.83291901949</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$83,A14,'Species'!$U$2:$U$83))</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>29871.676270239044</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.38</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>2398.83291901949</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
-        <x:v>29871.676270239044</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>644.5367584113</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.0388403075788193</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>10.935541865678129</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>644.5367584113</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>11.224142900801288</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$83,A15,'Species'!$U$2:$U$83))</x:f>
-        <x:v>7234.372681227667</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.0388403075788193</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>10.935541865678129</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>7048.3587055752405</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>186.01397565242678</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0263911051384615</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.02639110513846153</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>242.10952559999998</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>50.11872336272725</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>242.10952559999998</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>50.11872336272725</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$83,A16,'Species'!$U$2:$U$83))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>12134.220337027531</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>50.11872336272725</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>12134.220337027531</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>53.651023921000004</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.3899190365224636</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>245.4251338501026</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>53.651023921000004</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>252.07914905647843</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$83,A17,'Species'!$U$2:$U$83))</x:f>
-        <x:v>13524.30445601445</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.3899190365224636</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>245.4251338501026</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>13167.309727006483</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>356.9947290079672</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0271121995615977</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.02711219956159777</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>214820.07788741766</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.6331036961361396</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>429.63899906918107</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>214820.07788741766</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>546.1845829699884</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$83,A18,'Species'!$U$2:$U$83))</x:f>
-        <x:v>117331414.65451963</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.6331036961361396</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>429.63899906918107</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>92295083.24351364</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>25036331.41100599</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.2712639777890389</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.271263977789039</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>1891.0480467080001</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>630.957344480193</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>1891.0480467080001</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$83,A19,'Species'!$U$2:$U$83))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>1193170.6538353357</x:v>
       </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.8</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>1193170.6538353357</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G19">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O19">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2bc11d968db4ebf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31ba3d54ef6247d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8055,7 +6921,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -8154,7 +7020,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>1781327374.0574036</x:v>
+        <x:v>1391978413.5491133</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8168,7 +7034,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>1781327374.0574033</x:v>
+        <x:v>1468317274.3697884</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8182,7 +7048,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-389348960.5082903</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8196,7 +7062,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-2.384185791015625e-7</x:v>
+        <x:v>-313010099.68761516</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8207,9 +7073,9 @@
         <x:v>EEZ_959</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -8221,47 +7087,19 @@
         <x:v>EEZ_959</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_959</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_959</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2840ae3408ae4fef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R390c7262f15f4637"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8308,7 +7146,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
